--- a/01_mega_project_1_underwriting_approval/sample_reports/SAMPLE_notebook_03_workbook.xlsx
+++ b/01_mega_project_1_underwriting_approval/sample_reports/SAMPLE_notebook_03_workbook.xlsx
@@ -212,8 +212,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TSHAPFeatureImportanc" displayName="TSHAPFeatureImportanc" ref="A1:B39" headerRowCount="1">
-  <autoFilter ref="A1:B39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TSHAPFeatureImportanc" displayName="TSHAPFeatureImportanc" ref="A1:B57" headerRowCount="1">
+  <autoFilter ref="A1:B57"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Feature"/>
     <tableColumn id="2" name="Mean |SHAP|"/>
@@ -645,13 +645,13 @@
         <v>800</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01375</v>
+        <v>0.01125</v>
       </c>
       <c r="D2" t="n">
-        <v>584.3036230482276</v>
+        <v>587.6900009653294</v>
       </c>
       <c r="E2" t="n">
-        <v>345437824</v>
+        <v>343270048</v>
       </c>
     </row>
     <row r="3">
@@ -664,13 +664,13 @@
         <v>800</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02625</v>
+        <v>0.02</v>
       </c>
       <c r="D3" t="n">
-        <v>551.9918822628416</v>
+        <v>554.053759699912</v>
       </c>
       <c r="E3" t="n">
-        <v>354032416</v>
+        <v>353479264</v>
       </c>
     </row>
     <row r="4">
@@ -683,13 +683,13 @@
         <v>800</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0175</v>
+        <v>0.015</v>
       </c>
       <c r="D4" t="n">
-        <v>564.3138885517095</v>
+        <v>566.9974655316386</v>
       </c>
       <c r="E4" t="n">
-        <v>341143392</v>
+        <v>348698688</v>
       </c>
     </row>
     <row r="5">
@@ -702,13 +702,13 @@
         <v>800</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03375</v>
+        <v>0.045</v>
       </c>
       <c r="D5" t="n">
-        <v>537.8050390857943</v>
+        <v>538.6433398350185</v>
       </c>
       <c r="E5" t="n">
-        <v>339248224</v>
+        <v>333997760</v>
       </c>
     </row>
     <row r="6">
@@ -724,10 +724,10 @@
         <v>0.76125</v>
       </c>
       <c r="D6" t="n">
-        <v>488.7084331757967</v>
+        <v>486.8762486086098</v>
       </c>
       <c r="E6" t="n">
-        <v>346318656</v>
+        <v>346734752</v>
       </c>
     </row>
   </sheetData>
@@ -756,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2534144222736359</v>
+        <v>0.2521668076515198</v>
       </c>
     </row>
     <row r="3">
@@ -792,27 +792,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1743898093700409</v>
+        <v>0.1747947484254837</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DAYS_LAST_PHONE_CHANGE</t>
+          <t>INSTAL_PCT_LATE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1412617564201355</v>
+        <v>0.1330026388168335</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BUREAU_AMT_CREDIT_SUM_TOTAL</t>
+          <t>DAYS_LAST_PHONE_CHANGE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1375254392623901</v>
+        <v>0.1103271767497063</v>
       </c>
     </row>
     <row r="6">
@@ -822,341 +822,521 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1125814318656921</v>
+        <v>0.1078536212444305</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BUREAU_DAYS_CREDIT_MIN</t>
+          <t>YEARS_EMPLOYED</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.110224187374115</v>
+        <v>0.1047749146819115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>YEARS_EMPLOYED</t>
+          <t>AMT_ANNUITY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1093863546848297</v>
+        <v>0.1040008217096329</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AMT_INCOME_TOTAL</t>
+          <t>BUREAU_AMT_CREDIT_SUM_TOTAL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1079775616526604</v>
+        <v>0.09977433830499649</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ANNUITY_TO_CREDIT_RATIO</t>
+          <t>PREVAPP_DAYS_SINCE_LAST_DECISION</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1041649654507637</v>
+        <v>0.09657402336597443</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CREDIT_TO_INCOME_RATIO</t>
+          <t>ANNUITY_TO_INCOME_RATIO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1032789722084999</v>
+        <v>0.09385950118303299</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AMT_ANNUITY</t>
+          <t>BUREAU_AMT_CREDIT_SUM_DEBT_TOTAL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1030881702899933</v>
+        <v>0.0927639976143837</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ANNUITY_TO_INCOME_RATIO</t>
+          <t>ANNUITY_TO_CREDIT_RATIO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09611289203166962</v>
+        <v>0.09179290384054184</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BUREAU_AMT_CREDIT_SUM_DEBT_TOTAL</t>
+          <t>INSTAL_CNT_PAYMENTS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09578824788331985</v>
+        <v>0.08790147304534912</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>REGION_POPULATION_RELATIVE</t>
+          <t>PREVAPP_MEAN_AMT_APPLICATION</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08091460168361664</v>
+        <v>0.08710919320583344</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXT_SOURCE_1</t>
+          <t>CREDIT_TO_INCOME_RATIO</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.07462659478187561</v>
+        <v>0.08326031267642975</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMT_REQ_CREDIT_BUREAU_YEAR</t>
+          <t>AMT_INCOME_TOTAL</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.07372608035802841</v>
+        <v>0.08311517536640167</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NAME_HOUSING_TYPE</t>
+          <t>INSTAL_MEAN_PAYMENT_RATIO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.07120838016271591</v>
+        <v>0.07160167396068573</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMT_GOODS_PRICE</t>
+          <t>AMT_REQ_CREDIT_BUREAU_YEAR</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.06821639835834503</v>
+        <v>0.06796848773956299</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CNT_CHILDREN</t>
+          <t>REGION_POPULATION_RELATIVE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.06424444168806076</v>
+        <v>0.06776068359613419</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AMT_CREDIT</t>
+          <t>NAME_HOUSING_TYPE</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.05756999179720879</v>
+        <v>0.05500495433807373</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BUREAU_CNT_CREDITS</t>
+          <t>PREVAPP_MEAN_AMT_ANNUITY</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.05324937030673027</v>
+        <v>0.05487873777747154</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CNT_FAM_MEMBERS</t>
+          <t>EXT_SOURCE_1</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.04889578372240067</v>
+        <v>0.05391699448227882</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OCCUPATION_TYPE</t>
+          <t>PREVAPP_MEAN_AMT_CREDIT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.04302457720041275</v>
+        <v>0.05310070142149925</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>REGION_RATING_CLIENT</t>
+          <t>INSTAL_MEAN_DAYS_LATE_WHEN_LATE</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.03863221034407616</v>
+        <v>0.05164386332035065</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EXT_SOURCE_3</t>
+          <t>CNT_FAM_MEMBERS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.03832365572452545</v>
+        <v>0.0507521741092205</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NAME_FAMILY_STATUS</t>
+          <t>POS_MEAN_SK_DPD_DEF</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.03764402866363525</v>
+        <v>0.04908290505409241</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NAME_INCOME_TYPE</t>
+          <t>AMT_GOODS_PRICE</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.03590750321745872</v>
+        <v>0.04729103669524193</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FLAG_OWN_CAR</t>
+          <t>AMT_CREDIT</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.03489640727639198</v>
+        <v>0.04475238546729088</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CODE_GENDER</t>
+          <t>CNT_CHILDREN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.03258922323584557</v>
+        <v>0.04361832141876221</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BUREAU_AMT_OVERDUE_TOTAL</t>
+          <t>BUREAU_CNT_CREDITS</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.03057714179158211</v>
+        <v>0.04354960471391678</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NAME_EDUCATION_TYPE</t>
+          <t>CC_CNT_RECORDS</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.02989952452480793</v>
+        <v>0.04000998288393021</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BUREAU_CNT_ACTIVE</t>
+          <t>POS_CNT_RECORDS</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.02645721659064293</v>
+        <v>0.0389561802148819</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>OBS_30_CNT_SOCIAL_CIRCLE</t>
+          <t>POS_CNT_COMPLETED</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.02339441701769829</v>
+        <v>0.03631070628762245</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BUREAU_MAX_DAYS_OVERDUE</t>
+          <t>CC_MEAN_BALANCE</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.01220790576189756</v>
+        <v>0.03135154023766518</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FLAG_OWN_REALTY</t>
+          <t>BUREAU_TOTAL_DPD_MONTHS</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.01084640435874462</v>
+        <v>0.0312844030559063</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NAME_CONTRACT_TYPE</t>
+          <t>EXT_SOURCE_3</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.004544856958091259</v>
+        <v>0.03007679060101509</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DEF_30_CNT_SOCIAL_CIRCLE</t>
+          <t>REGION_RATING_CLIENT</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.0038456991314888</v>
+        <v>0.02846934646368027</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BUREAU_CNT_PROLONGED</t>
+          <t>CODE_GENDER</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.003811221104115248</v>
+        <v>0.02817976288497448</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CC_MEAN_UTILIZATION</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.02687168680131435</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>OCCUPATION_TYPE</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.02367966249585152</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PREVAPP_APPROVAL_RATE</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.02275821380317211</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NAME_INCOME_TYPE</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.02263196930289268</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>NAME_FAMILY_STATUS</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.02191457897424698</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FLAG_OWN_CAR</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.02029421180486679</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NAME_EDUCATION_TYPE</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.01966172270476818</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PREVAPP_REFUSAL_RATE</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.01882682554423809</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BUREAU_CNT_ACTIVE</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.01737139746546745</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PREVAPP_CNT_APPROVED</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.01717385649681091</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>OBS_30_CNT_SOCIAL_CIRCLE</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.01458358764648438</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BUREAU_MAX_DAYS_OVERDUE</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.01405974198132753</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PREVAPP_CNT_TOTAL</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.008971106261014938</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CC_SUM_SK_DPD</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.007206067442893982</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>FLAG_OWN_REALTY</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.00669976556673646</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>DEF_30_CNT_SOCIAL_CIRCLE</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.003163618734106421</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PREVAPP_CNT_REFUSED</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.002594201592728496</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NAME_CONTRACT_TYPE</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.002078242832794785</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B39">
+  <conditionalFormatting sqref="B2:B57">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1214,11 +1394,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EXT_SOURCE_2 &lt;= 0.24</t>
+          <t>EXT_SOURCE_2 &gt; 0.74</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.05536389210397303</v>
+        <v>-0.0455622393331411</v>
       </c>
     </row>
     <row r="3">
@@ -1229,11 +1409,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AGE_YEARS &gt; 57.56</t>
+          <t>INSTAL_PCT_LATE &gt; 0.37</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.03715593417512436</v>
+        <v>-0.04165546031360286</v>
       </c>
     </row>
     <row r="4">
@@ -1244,11 +1424,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EXT_SOURCE_3 &lt;= 0.49</t>
+          <t>AGE_YEARS &gt; 57.56</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.02640977130822969</v>
+        <v>0.04005799337897929</v>
       </c>
     </row>
     <row r="5">
@@ -1259,11 +1439,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>REGION_POPULATION_RELATIVE &lt;= 0.02</t>
+          <t>DAYS_LAST_PHONE_CHANGE &lt;= -3042.25</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.02583417012003419</v>
+        <v>0.03647904760764295</v>
       </c>
     </row>
     <row r="6">
@@ -1274,11 +1454,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMT_ANNUITY &lt;= 12373.48</t>
+          <t>INSTAL_CNT_PAYMENTS &gt; 32.00</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.02326868821334543</v>
+        <v>-0.02368554919712777</v>
       </c>
     </row>
     <row r="7">
@@ -1289,11 +1469,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BUREAU_AMT_OVERDUE_TOTAL &lt;= 0.00</t>
+          <t>INSTAL_MEAN_PAYMENT_RATIO &gt; 0.94</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02315270280746589</v>
+        <v>0.02283199525564552</v>
       </c>
     </row>
     <row r="8">
@@ -1304,11 +1484,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.09 &lt; BUREAU_DEBT_TO_CREDIT_RATIO &lt;= 0.26</t>
+          <t>POS_MEAN_SK_DPD_DEF &lt;= 0.00</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.02034331111717656</v>
+        <v>-0.0216650093963495</v>
       </c>
     </row>
     <row r="9">
@@ -1319,11 +1499,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CNT_CHILDREN &lt;= 0.00</t>
+          <t>PREVAPP_MEAN_AMT_APPLICATION &gt; 150964.04</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.01922618874202021</v>
+        <v>-0.01704225721017109</v>
       </c>
     </row>
     <row r="10">
@@ -1334,11 +1514,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BUREAU_DEBT_TO_CREDIT_RATIO &gt; 0.26</t>
+          <t>EXT_SOURCE_2 &gt; 0.74</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.0535768499032132</v>
+        <v>-0.04390743191003788</v>
       </c>
     </row>
     <row r="11">
@@ -1349,11 +1529,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EXT_SOURCE_2 &gt; 0.74</t>
+          <t>BUREAU_DEBT_TO_CREDIT_RATIO &gt; 0.26</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.05274482119497263</v>
+        <v>-0.04061742589236837</v>
       </c>
     </row>
     <row r="12">
@@ -1364,11 +1544,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BUREAU_AMT_CREDIT_SUM_DEBT_TOTAL &gt; 46142.76</t>
+          <t>POS_MEAN_SK_DPD_DEF &lt;= 0.00</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.02509814013556741</v>
+        <v>-0.03058195249639287</v>
       </c>
     </row>
     <row r="13">
@@ -1379,11 +1559,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMT_INCOME_TOTAL &lt;= 94742.04</t>
+          <t>CREDIT_TO_INCOME_RATIO &gt; 4.72</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02247995337464653</v>
+        <v>-0.02545854528093011</v>
       </c>
     </row>
     <row r="14">
@@ -1394,11 +1574,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NAME_HOUSING_TYPE=0</t>
+          <t>EXT_SOURCE_3 &lt;= 0.49</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.02086600990473495</v>
+        <v>0.02111145151623721</v>
       </c>
     </row>
     <row r="15">
@@ -1409,11 +1589,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EXT_SOURCE_3 &lt;= 0.49</t>
+          <t>BUREAU_AMT_CREDIT_SUM_DEBT_TOTAL &gt; 46142.76</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.01991798264638332</v>
+        <v>-0.0193984631204407</v>
       </c>
     </row>
     <row r="16">
@@ -1424,11 +1604,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CREDIT_TO_INCOME_RATIO &gt; 4.72</t>
+          <t>94353.71 &lt; PREVAPP_MEAN_AMT_APPLICATION &lt;= 150964.04</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.01733182581471819</v>
+        <v>-0.01643766250332473</v>
       </c>
     </row>
     <row r="17">
@@ -1439,11 +1619,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BUREAU_AMT_OVERDUE_TOTAL &lt;= 0.00</t>
+          <t>0.03 &lt; REGION_POPULATION_RELATIVE &lt;= 0.05</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0158531146859024</v>
+        <v>-0.01534635605880993</v>
       </c>
     </row>
     <row r="18">
@@ -1454,11 +1634,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.24 &lt; EXT_SOURCE_2 &lt;= 0.49</t>
+          <t>AGE_YEARS &gt; 57.56</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03067793789480528</v>
+        <v>0.0397991375483051</v>
       </c>
     </row>
     <row r="19">
@@ -1469,11 +1649,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EXT_SOURCE_3 &lt;= 0.49</t>
+          <t>POS_MEAN_SK_DPD_DEF &lt;= 0.00</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02494405554849701</v>
+        <v>-0.03429936011616579</v>
       </c>
     </row>
     <row r="20">
@@ -1484,11 +1664,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>REGION_POPULATION_RELATIVE &lt;= 0.02</t>
+          <t>0.49 &lt; EXT_SOURCE_2 &lt;= 0.74</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0212781057641398</v>
+        <v>-0.0292325775949109</v>
       </c>
     </row>
     <row r="21">
@@ -1499,11 +1679,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.09 &lt; BUREAU_DEBT_TO_CREDIT_RATIO &lt;= 0.26</t>
+          <t>INSTAL_CNT_PAYMENTS &gt; 32.00</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.01893487604928105</v>
+        <v>-0.02329774406345093</v>
       </c>
     </row>
     <row r="22">
@@ -1514,11 +1694,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CNT_CHILDREN &lt;= 0.00</t>
+          <t>INSTAL_MEAN_PAYMENT_RATIO &gt; 0.94</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.01850539104114034</v>
+        <v>0.02160880704319321</v>
       </c>
     </row>
     <row r="23">
@@ -1529,11 +1709,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>OCCUPATION_TYPE=4</t>
+          <t>EXT_SOURCE_3 &lt;= 0.49</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.01802814605402099</v>
+        <v>0.01981697866444678</v>
       </c>
     </row>
     <row r="24">
@@ -1544,11 +1724,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>REGION_RATING_CLIENT &lt;= 1.00</t>
+          <t>3472.36 &lt; BUREAU_AMT_CREDIT_SUM_DEBT_TOTAL &lt;= 16357.52</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.01443806131976434</v>
+        <v>0.01736646773055311</v>
       </c>
     </row>
     <row r="25">
@@ -1559,11 +1739,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NAME_HOUSING_TYPE=3</t>
+          <t>PREVAPP_MEAN_AMT_APPLICATION &lt;= 47323.38</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01321209063713714</v>
+        <v>0.01672716862735176</v>
       </c>
     </row>
   </sheetData>
@@ -1616,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02637987397611141</v>
+        <v>0.02355502545833588</v>
       </c>
       <c r="C2" t="n">
         <v>0.01</v>
@@ -1630,10 +1810,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.04388986900448799</v>
+        <v>0.03927225992083549</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0175</v>
+        <v>0.0125</v>
       </c>
       <c r="D3" t="n">
         <v>400</v>
@@ -1644,10 +1824,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.05802986025810242</v>
+        <v>0.05297127738595009</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D4" t="n">
         <v>400</v>
@@ -1658,7 +1838,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.07180288434028625</v>
+        <v>0.0660737007856369</v>
       </c>
       <c r="C5" t="n">
         <v>0.015</v>
@@ -1672,10 +1852,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.08681906014680862</v>
+        <v>0.08050086349248886</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0275</v>
+        <v>0.0125</v>
       </c>
       <c r="D6" t="n">
         <v>400</v>
@@ -1686,10 +1866,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1052267476916313</v>
+        <v>0.09972450137138367</v>
       </c>
       <c r="C7" t="n">
-        <v>0.025</v>
+        <v>0.0275</v>
       </c>
       <c r="D7" t="n">
         <v>400</v>
@@ -1700,10 +1880,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1286390274763107</v>
+        <v>0.1248630210757256</v>
       </c>
       <c r="C8" t="n">
-        <v>0.025</v>
+        <v>0.0225</v>
       </c>
       <c r="D8" t="n">
         <v>400</v>
@@ -1714,10 +1894,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1688621640205383</v>
+        <v>0.1656050235033035</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0425</v>
+        <v>0.0675</v>
       </c>
       <c r="D9" t="n">
         <v>400</v>
@@ -1728,10 +1908,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.3441287577152252</v>
+        <v>0.3505840301513672</v>
       </c>
       <c r="C10" t="n">
-        <v>0.53</v>
+        <v>0.5225</v>
       </c>
       <c r="D10" t="n">
         <v>400</v>
@@ -1742,10 +1922,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6358301043510437</v>
+        <v>0.6581264734268188</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9925</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>400</v>
@@ -2062,28 +2242,28 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="8" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Problem 1's XGBoost model does not yet meet the scorecard deployment bar</t>
+          <t>Problem 1's XGBoost model meets the scorecard deployment bar</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Score AUC 0.9521 (95% bootstrap CI [0.9385, 0.9631]); deployment checks 3/4 PASS.</t>
+          <t>Score AUC 0.9591 (95% bootstrap CI [0.9468, 0.9696]); deployment checks 4/4 PASS.</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Calibration gap 0.1050 vs. &lt;0.1 threshold; split-half PSI 0.0003 vs. &lt;0.1 threshold.</t>
+          <t>Calibration gap 0.0984 vs. &lt;0.1 threshold; split-half PSI 0.0008 vs. &lt;0.1 threshold.</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>Investigate the failing check(s) above before promoting to production; re-run this notebook after any fix to confirm.</t>
+          <t>No further tuning required this cycle.</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
@@ -2143,12 +2323,12 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Real default rate 76.12% in the 'Very Poor' band vs. 1.38% in 'Excellent'.</t>
+          <t>Real default rate 76.12% in the 'Very Poor' band vs. 1.12% in 'Excellent'.</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>$346,318,656 of real portfolio volume sits in this highest-risk band.</t>
+          <t>$346,734,752 of real portfolio volume sits in this highest-risk band.</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
